--- a/public/templates/Shablloni-3-Faqe.xlsx
+++ b/public/templates/Shablloni-3-Faqe.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Graniti\Te Qafa\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\AAB\Viti 3 Semestri 6\Tema-Graniti\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C265EB0-1397-449A-AADA-C6EF283D8BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B24944FA-DB16-4B69-B05C-BAE3D4B6B059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -533,7 +533,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -585,14 +585,8 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -644,12 +638,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -676,6 +664,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1000,18 +997,18 @@
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="3"/>
-      <c r="F1" s="42" t="s">
+      <c r="F1" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="42"/>
-      <c r="H1" s="43"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="41"/>
     </row>
     <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="5"/>
-      <c r="G2" s="36"/>
+      <c r="G2" s="35"/>
       <c r="H2" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1019,34 +1016,35 @@
         <v>7</v>
       </c>
       <c r="E3" s="5"/>
-      <c r="F3" s="56" t="s">
+      <c r="F3" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="56"/>
-      <c r="H3" s="57"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="65"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
-      <c r="C4" s="37"/>
+      <c r="C4" s="36"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="57"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="65"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="35"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="65"/>
     </row>
     <row r="6" spans="1:8" ht="21" x14ac:dyDescent="0.4">
       <c r="A6" s="34" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="5"/>
-      <c r="F6" s="4"/>
-      <c r="H6" s="5"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="65"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
@@ -1072,13 +1070,13 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="58" t="s">
+      <c r="A9" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="59"/>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="60"/>
+      <c r="B9" s="55"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="55"/>
+      <c r="E9" s="56"/>
       <c r="F9" s="14" t="s">
         <v>6</v>
       </c>
@@ -1088,23 +1086,23 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="58"/>
-      <c r="B10" s="59"/>
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="60"/>
+      <c r="A10" s="54"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="56"/>
       <c r="F10" s="4"/>
       <c r="G10" s="5"/>
       <c r="H10" s="10"/>
     </row>
     <row r="11" spans="1:8" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="61" t="s">
+      <c r="A11" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="62"/>
-      <c r="C11" s="62"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="63"/>
+      <c r="B11" s="58"/>
+      <c r="C11" s="58"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="59"/>
       <c r="F11" s="4" t="s">
         <v>26</v>
       </c>
@@ -1114,14 +1112,14 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="64"/>
-      <c r="B12" s="65"/>
-      <c r="C12" s="65"/>
-      <c r="D12" s="65"/>
-      <c r="E12" s="66"/>
+      <c r="A12" s="60"/>
+      <c r="B12" s="61"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="62"/>
       <c r="F12" s="15"/>
       <c r="G12" s="16"/>
-      <c r="H12" s="41"/>
+      <c r="H12" s="39"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
@@ -1131,11 +1129,11 @@
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="47" t="s">
+      <c r="F13" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="48"/>
-      <c r="H13" s="49"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="47"/>
     </row>
     <row r="14" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
@@ -1147,9 +1145,9 @@
       <c r="E14" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="50"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="52"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="50"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
@@ -1172,42 +1170,42 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="44" t="s">
+      <c r="A16" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="45"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="46"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="44"/>
       <c r="F16" s="4"/>
       <c r="G16" s="5"/>
       <c r="H16" s="10"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="44"/>
-      <c r="B17" s="45"/>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="46"/>
+      <c r="A17" s="42"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="44"/>
       <c r="F17" s="4"/>
       <c r="G17" s="5"/>
       <c r="H17" s="10"/>
     </row>
     <row r="18" spans="1:8" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="44"/>
-      <c r="B18" s="45"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="46"/>
+      <c r="A18" s="42"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="44"/>
       <c r="F18" s="4"/>
       <c r="G18" s="5"/>
       <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="19"/>
-      <c r="B19" s="39"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
+      <c r="B19" s="37"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
       <c r="E19" s="21" t="s">
         <v>32</v>
       </c>
@@ -1219,9 +1217,9 @@
     </row>
     <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="19"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
+      <c r="B20" s="37"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
       <c r="E20" s="22" t="s">
         <v>18</v>
       </c>
@@ -1234,9 +1232,9 @@
     </row>
     <row r="21" spans="1:8" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
       <c r="E21" s="20"/>
       <c r="F21" s="31"/>
       <c r="G21" s="32"/>
@@ -1244,41 +1242,41 @@
     </row>
     <row r="22" spans="1:8" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="23"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
       <c r="E22" s="24"/>
       <c r="F22" s="31"/>
       <c r="G22" s="32"/>
       <c r="H22" s="33"/>
     </row>
     <row r="23" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="53" t="s">
+      <c r="A23" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="54"/>
-      <c r="C23" s="54"/>
-      <c r="D23" s="54"/>
-      <c r="E23" s="55"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="53"/>
       <c r="F23" s="31"/>
       <c r="G23" s="32"/>
       <c r="H23" s="33"/>
     </row>
     <row r="24" spans="1:8" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="53"/>
-      <c r="B24" s="54"/>
-      <c r="C24" s="54"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="55"/>
+      <c r="A24" s="51"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="53"/>
       <c r="F24" s="31"/>
       <c r="G24" s="32"/>
       <c r="H24" s="33"/>
     </row>
     <row r="25" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="23"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="40"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
       <c r="E25" s="21" t="s">
         <v>33</v>
       </c>
@@ -1290,9 +1288,9 @@
     </row>
     <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="23"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
       <c r="E26" s="22" t="s">
         <v>18</v>
       </c>
@@ -1305,41 +1303,41 @@
     </row>
     <row r="27" spans="1:8" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="23"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
       <c r="E27" s="24"/>
       <c r="F27" s="31"/>
       <c r="G27" s="32"/>
       <c r="H27" s="33"/>
     </row>
     <row r="28" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="53" t="s">
+      <c r="A28" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="54"/>
-      <c r="C28" s="54"/>
-      <c r="D28" s="54"/>
-      <c r="E28" s="55"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="53"/>
       <c r="F28" s="31"/>
       <c r="G28" s="32"/>
       <c r="H28" s="33"/>
     </row>
     <row r="29" spans="1:8" ht="139.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="53"/>
-      <c r="B29" s="54"/>
-      <c r="C29" s="54"/>
-      <c r="D29" s="54"/>
-      <c r="E29" s="55"/>
+      <c r="A29" s="51"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="53"/>
       <c r="F29" s="31"/>
       <c r="G29" s="32"/>
       <c r="H29" s="33"/>
     </row>
     <row r="30" spans="1:8" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="23"/>
-      <c r="B30" s="40"/>
-      <c r="C30" s="40"/>
-      <c r="D30" s="40"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
       <c r="E30" s="21" t="s">
         <v>34</v>
       </c>
@@ -1351,9 +1349,9 @@
     </row>
     <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="23"/>
-      <c r="B31" s="40"/>
-      <c r="C31" s="40"/>
-      <c r="D31" s="40"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="38"/>
+      <c r="D31" s="38"/>
       <c r="E31" s="22" t="s">
         <v>18</v>
       </c>
@@ -1366,9 +1364,9 @@
     </row>
     <row r="32" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="19"/>
-      <c r="B32" s="39"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
+      <c r="B32" s="37"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="37"/>
       <c r="E32" s="21"/>
       <c r="F32" s="25"/>
       <c r="G32" s="26"/>
@@ -1376,9 +1374,9 @@
     </row>
     <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="19"/>
-      <c r="B33" s="39"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
+      <c r="B33" s="37"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="37"/>
       <c r="E33" s="5"/>
       <c r="F33" s="4"/>
       <c r="G33" s="5"/>
@@ -1437,9 +1435,9 @@
     <mergeCell ref="F13:H14"/>
     <mergeCell ref="A23:E24"/>
     <mergeCell ref="A28:E29"/>
-    <mergeCell ref="F3:H4"/>
     <mergeCell ref="A9:E10"/>
     <mergeCell ref="A11:E12"/>
+    <mergeCell ref="F3:H6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="92" orientation="portrait" r:id="rId1"/>
